--- a/data/trans_camb/MCS12_SP_R3-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/MCS12_SP_R3-Estudios-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en el primer cuartil de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población en el primer cuartil (48.388) de la puntuación del componente de salud mental (SF12)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 6,71</t>
+          <t>-1,44; 6,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 3,17</t>
+          <t>-5,29; 3,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 5,06</t>
+          <t>-4,3; 5,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,55; 11,18</t>
+          <t>3,4; 10,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 9,76</t>
+          <t>2,27; 10,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 10,77</t>
+          <t>3,22; 10,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 8,36</t>
+          <t>2,48; 8,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 5,84</t>
+          <t>-0,04; 6,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 7,5</t>
+          <t>1,46; 7,34</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 26,52</t>
+          <t>-4,83; 27,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-18,33; 12,69</t>
+          <t>-18,67; 12,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,95; 20,5</t>
+          <t>-14,97; 21,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,78; 36,61</t>
+          <t>9,63; 35,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 31,48</t>
+          <t>6,63; 33,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,56; 34,36</t>
+          <t>9,13; 34,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,12; 28,39</t>
+          <t>7,24; 27,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 20,21</t>
+          <t>-0,16; 20,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 25,75</t>
+          <t>4,64; 25,15</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,7; 8,95</t>
+          <t>4,03; 9,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 5,09</t>
+          <t>0,22; 4,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 4,48</t>
+          <t>-3,74; 4,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,15; 10,35</t>
+          <t>3,93; 10,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 2,72</t>
+          <t>-3,18; 2,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 26,24</t>
+          <t>-0,68; 27,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,4; 8,55</t>
+          <t>4,82; 8,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 3,2</t>
+          <t>-0,65; 3,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 17,59</t>
+          <t>-0,34; 17,88</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,38; 68,36</t>
+          <t>24,63; 67,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 39,35</t>
+          <t>1,74; 36,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-25,18; 32,07</t>
+          <t>-24,45; 33,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,98; 48,42</t>
+          <t>16,32; 49,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 12,93</t>
+          <t>-12,84; 12,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 120,66</t>
+          <t>-2,96; 119,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,0; 48,11</t>
+          <t>24,23; 49,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 18,25</t>
+          <t>-3,3; 17,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 94,51</t>
+          <t>-1,71; 98,6</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 1,83</t>
+          <t>-6,97; 2,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 4,64</t>
+          <t>-4,37; 4,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 9,48</t>
+          <t>-0,87; 9,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 4,18</t>
+          <t>-7,14; 4,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 3,41</t>
+          <t>-6,97; 3,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 6,63</t>
+          <t>-3,52; 6,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 1,85</t>
+          <t>-5,65; 1,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 2,76</t>
+          <t>-3,98; 3,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 6,65</t>
+          <t>-0,21; 6,57</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-39,51; 15,3</t>
+          <t>-39,38; 20,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-24,97; 34,19</t>
+          <t>-25,25; 37,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 68,66</t>
+          <t>-6,63; 71,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-28,31; 21,99</t>
+          <t>-28,5; 21,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,29; 17,89</t>
+          <t>-27,77; 19,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 35,87</t>
+          <t>-13,74; 34,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,24; 11,06</t>
+          <t>-27,54; 9,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-20,59; 16,68</t>
+          <t>-19,41; 17,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 39,38</t>
+          <t>-1,31; 38,98</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,73</t>
+          <t>1,51; 5,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 2,12</t>
+          <t>-1,65; 2,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 2,12</t>
+          <t>-4,67; 2,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,79; 8,32</t>
+          <t>3,95; 8,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 2,32</t>
+          <t>-1,96; 2,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 19,91</t>
+          <t>-0,37; 17,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,43; 6,5</t>
+          <t>3,38; 6,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,83</t>
+          <t>-1,29; 1,72</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 9,35</t>
+          <t>-1,04; 11,4</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,41; 32,73</t>
+          <t>7,67; 31,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 12,02</t>
+          <t>-8,53; 12,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-23,17; 11,81</t>
+          <t>-23,86; 11,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,77; 32,78</t>
+          <t>14,2; 32,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 9,16</t>
+          <t>-7,16; 9,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 75,21</t>
+          <t>-1,41; 68,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,72; 30,04</t>
+          <t>14,4; 29,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 8,54</t>
+          <t>-5,54; 7,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 42,37</t>
+          <t>-4,51; 50,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/MCS12_SP_R3-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/MCS12_SP_R3-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>-0,68</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,82</t>
+          <t>6,87</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,44</t>
+          <t>3,88</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 6,78</t>
+          <t>-1,21; 7,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 3,18</t>
+          <t>-5,06; 2,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 5,26</t>
+          <t>-5,15; 3,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,4; 10,89</t>
+          <t>3,59; 11,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 10,32</t>
+          <t>1,95; 9,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,22; 10,62</t>
+          <t>3,54; 10,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 8,13</t>
+          <t>2,34; 8,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 6,04</t>
+          <t>0,19; 6,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 7,34</t>
+          <t>1,07; 6,5</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>-2,51%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 27,06</t>
+          <t>-4,19; 27,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-18,67; 12,91</t>
+          <t>-17,41; 11,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,97; 21,12</t>
+          <t>-17,88; 13,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,63; 35,2</t>
+          <t>10,54; 36,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,63; 33,63</t>
+          <t>5,54; 31,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,13; 34,52</t>
+          <t>10,36; 34,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,24; 27,73</t>
+          <t>7,34; 27,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 20,76</t>
+          <t>0,57; 21,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,64; 25,15</t>
+          <t>3,78; 22,62</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,36</t>
+          <t>3,66</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,36</t>
+          <t>1,77</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4,42</t>
+          <t>2,81</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,03; 9,08</t>
+          <t>3,54; 8,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 4,94</t>
+          <t>0,04; 4,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 4,53</t>
+          <t>1,17; 6,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,93; 10,52</t>
+          <t>4,2; 10,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 2,69</t>
+          <t>-3,15; 2,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 27,0</t>
+          <t>-0,97; 4,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,82; 8,76</t>
+          <t>4,71; 8,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 3,05</t>
+          <t>-0,69; 3,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 17,88</t>
+          <t>0,8; 4,64</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,63; 67,23</t>
+          <t>21,82; 66,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 36,83</t>
+          <t>-0,22; 36,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-24,45; 33,08</t>
+          <t>7,14; 45,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,32; 49,32</t>
+          <t>17,05; 48,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 12,92</t>
+          <t>-12,95; 11,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 119,21</t>
+          <t>-4,07; 21,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,23; 49,48</t>
+          <t>23,82; 50,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 17,2</t>
+          <t>-3,65; 17,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 98,6</t>
+          <t>4,22; 26,12</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,26</t>
+          <t>3,25</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,78</t>
+          <t>2,15</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,28</t>
+          <t>2,98</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 2,61</t>
+          <t>-6,92; 2,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 4,72</t>
+          <t>-4,25; 4,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 9,44</t>
+          <t>-1,39; 7,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 4,04</t>
+          <t>-6,58; 4,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 3,5</t>
+          <t>-6,85; 3,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 6,43</t>
+          <t>-2,43; 6,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 1,58</t>
+          <t>-5,46; 1,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 3,02</t>
+          <t>-3,83; 2,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 6,57</t>
+          <t>-0,18; 6,41</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-39,38; 20,71</t>
+          <t>-39,43; 17,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-25,25; 37,27</t>
+          <t>-24,38; 35,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 71,61</t>
+          <t>-8,11; 57,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-28,5; 21,64</t>
+          <t>-27,19; 23,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-27,77; 19,88</t>
+          <t>-27,53; 17,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-13,74; 34,35</t>
+          <t>-10,29; 36,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,54; 9,89</t>
+          <t>-26,94; 10,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-19,41; 17,56</t>
+          <t>-19,42; 15,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 38,98</t>
+          <t>-1,67; 37,66</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>1,0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,4</t>
+          <t>1,24</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,17</t>
+          <t>1,17</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 5,55</t>
+          <t>1,53; 5,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 2,26</t>
+          <t>-1,46; 2,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 2,16</t>
+          <t>-0,87; 2,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,95; 8,35</t>
+          <t>3,81; 8,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 2,31</t>
+          <t>-1,8; 2,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 17,52</t>
+          <t>-0,81; 2,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,38; 6,49</t>
+          <t>3,31; 6,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 1,72</t>
+          <t>-1,28; 1,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 11,4</t>
+          <t>-0,36; 2,51</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-1,58%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,67; 31,33</t>
+          <t>7,65; 31,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 12,89</t>
+          <t>-7,49; 12,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-23,86; 11,72</t>
+          <t>-4,44; 15,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,2; 32,99</t>
+          <t>13,77; 31,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 9,1</t>
+          <t>-6,48; 10,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 68,91</t>
+          <t>-2,97; 11,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,4; 29,66</t>
+          <t>14,33; 29,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 7,7</t>
+          <t>-5,47; 6,93</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 50,58</t>
+          <t>-1,57; 11,42</t>
         </is>
       </c>
     </row>
